--- a/branches/dependabot/github_actions/dev/actions-d025328a43/StructureDefinition-mii-pr-seltene-registerteilnahme.xlsx
+++ b/branches/dependabot/github_actions/dev/actions-d025328a43/StructureDefinition-mii-pr-seltene-registerteilnahme.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="864" uniqueCount="227">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="865" uniqueCount="227">
   <si>
     <t>Property</t>
   </si>
@@ -57,10 +57,13 @@
     <t>Experimental</t>
   </si>
   <si>
+    <t>false</t>
+  </si>
+  <si>
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T01:49:31+00:00</t>
+    <t>2026-09-14T01:49:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -118,9 +121,6 @@
   </si>
   <si>
     <t>Abstract</t>
-  </si>
-  <si>
-    <t>false</t>
   </si>
   <si>
     <t>Derivation</t>
@@ -463,10 +463,10 @@
     <t>Katalogeintrag des Registers als Library (optional)</t>
   </si>
   <si>
-    <t>Optionaler Verweis auf den Library-Katalogeintrag des Registers nach dem Profil mii-pr-studie-register des MII KDS Moduls Studie. Der verbindliche Registerbezug laeuft ueber ResearchSubject.study, das in R4 zwingend auf eine ResearchStudy zeigt.</t>
-  </si>
-  <si>
-    <t>Optionaler Verweis auf den Library-Katalogeintrag nach mii-pr-studie-register. Der verbindliche Registerbezug laeuft ueber study, weil R4 das so erzwingt.</t>
+    <t>Optionaler Verweis auf den Library-Katalogeintrag des Registers nach dem Profil mii-pr-studie-register des MII KDS Moduls Studie. Der verbindliche Registerbezug läuft über ResearchSubject.study, das in R4 zwingend auf eine ResearchStudy zeigt.</t>
+  </si>
+  <si>
+    <t>Optionaler Verweis auf den Library-Katalogeintrag nach mii-pr-studie-register. Der verbindliche Registerbezug läuft über study, weil R4 das so erzwingt.</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1
@@ -659,7 +659,7 @@
 </t>
   </si>
   <si>
-    <t>Das Register, als ResearchStudy gefuehrt</t>
+    <t>Das Register, als ResearchStudy geführt</t>
   </si>
   <si>
     <t>Reference to the study the subject is participating in.</t>
@@ -721,7 +721,7 @@
     <t>A record of the patient's informed agreement to participate in the study.</t>
   </si>
   <si>
-    <t>Eine Registeraufnahme beruht selbstverstaendlich auf einer Einwilligung — aber die liegt beim Registerbetreiber. Ein Standort, der die Teilnahme nur nachhaelt, kann sie nicht referenzieren. Die Angabe leer zu lassen bedeutet daher NICHT, dass keine Einwilligung existiert, sondern nur, dass sie hier nicht als FHIR-Ressource greifbar ist. Genau deshalb leitet dieses Profil nicht vom Probanden-Profil des Moduls Studie ab, das consent mit 1..1 fordert.</t>
+    <t>Eine Registeraufnahme beruht selbstverständlich auf einer Einwilligung — aber die liegt beim Registerbetreiber. Ein Standort, der die Teilnahme nur nachhält, kann sie nicht referenzieren. Die Angabe leer zu lassen bedeutet daher NICHT, dass keine Einwilligung existiert, sondern nur, dass sie hier nicht als FHIR-Ressource greifbar ist. Genau deshalb leitet dieses Profil nicht vom Probanden-Profil des Moduls Studie ab, das consent mit 1..1 fordert.</t>
   </si>
   <si>
     <t>ResearchStudy.consent is related to PerformedStudySubjectMilestone.informedConsentIndicator in that the informedConsentIndicator can be derived from the data in the Consent resource.</t>
@@ -932,98 +932,100 @@
       <c r="A7" t="s" s="2">
         <v>12</v>
       </c>
-      <c r="B7" s="2"/>
+      <c r="B7" t="s" s="2">
+        <v>13</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>34</v>
+        <v>13</v>
       </c>
     </row>
     <row r="20">
@@ -1209,10 +1211,10 @@
     </row>
     <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" t="s" s="2">
@@ -1294,7 +1296,7 @@
         <v>80</v>
       </c>
       <c r="AF2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AG2" t="s" s="2">
         <v>78</v>
